--- a/Tests Data/Kyocera KC200GT/Single-diode model/G = 511 W.m^-2 and T = 54.3 ºC/Single-diode emulator - Kyocera KC200GT (ref = STC, G = 511 and T = 54.3).xlsx
+++ b/Tests Data/Kyocera KC200GT/Single-diode model/G = 511 W.m^-2 and T = 54.3 ºC/Single-diode emulator - Kyocera KC200GT (ref = STC, G = 511 and T = 54.3).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\Test Data - new\Kyocera KC200GT\Single-diode model\G = 511 W.m^-2 and T = 54.3 ºC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\PV-emulator\Tests Data\Kyocera KC200GT\Single-diode model\G = 511 W.m^-2 and T = 54.3 ºC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79446136-C46E-4DF1-8ED4-41E31285B9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A139D6B-35A4-41FE-9A03-BDF38A6CCC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B8D570-ED79-418B-A1D1-0F000D275672}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -534,57 +534,57 @@
         <v>60</v>
       </c>
       <c r="B2">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="C2">
         <f>A2*B2</f>
-        <v>46.800000000000004</v>
+        <v>58.199999999999996</v>
       </c>
       <c r="D2">
-        <v>9.4499999999999993</v>
+        <v>12.22</v>
       </c>
       <c r="E2">
-        <v>4.01</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F2">
         <f>D2*E2</f>
-        <v>37.894499999999994</v>
+        <v>50.101999999999997</v>
       </c>
       <c r="G2">
         <f>D2/E2</f>
-        <v>2.3566084788029924</v>
+        <v>2.9804878048780492</v>
       </c>
       <c r="H2">
-        <v>30.409756000000002</v>
+        <v>30.799537999999998</v>
       </c>
       <c r="I2">
-        <v>12.985798000000001</v>
+        <v>10.383743000000001</v>
       </c>
       <c r="J2">
-        <v>9.8681750000000008</v>
+        <v>12.533917000000001</v>
       </c>
       <c r="K2">
-        <v>4.2139810000000004</v>
+        <v>4.2256790000000004</v>
       </c>
       <c r="L2">
         <f>J2/K2</f>
-        <v>2.3417701693481767</v>
+        <v>2.9661308868941534</v>
       </c>
       <c r="M2">
         <f>ABS(J2-D2)/D2*100</f>
-        <v>4.4251322751322917</v>
+        <v>2.5688788870703765</v>
       </c>
       <c r="N2">
         <f>ABS(K2-E2)/E2*100</f>
-        <v>5.0868079800498913</v>
+        <v>3.065341463414653</v>
       </c>
       <c r="O2">
-        <f>(ABS(L2-G2)/G2)*100</f>
-        <v>0.62964678215672887</v>
+        <f t="shared" ref="O2:O19" si="0">(ABS(L2-G2)/G2)*100</f>
+        <v>0.48169692089994159</v>
       </c>
       <c r="P2">
-        <f>(F2/C2)*100</f>
-        <v>80.971153846153825</v>
+        <f t="shared" ref="P2:P19" si="1">(F2/C2)*100</f>
+        <v>86.085910652920958</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -592,57 +592,57 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="C3">
         <f>A3*B3</f>
-        <v>60</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="D3">
-        <v>13.23</v>
+        <v>14.38</v>
       </c>
       <c r="E3" s="3">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="F3">
         <f>D3*E3</f>
-        <v>51.597000000000001</v>
+        <v>62.265400000000007</v>
       </c>
       <c r="G3">
         <f>D3/E3</f>
-        <v>3.3923076923076927</v>
+        <v>3.3210161662817552</v>
       </c>
       <c r="H3">
-        <v>30.408054</v>
+        <v>30.407264999999999</v>
       </c>
       <c r="I3">
-        <v>9.3825470000000006</v>
+        <v>8.7217599999999997</v>
       </c>
       <c r="J3">
-        <v>13.614193</v>
+        <v>14.705232000000001</v>
       </c>
       <c r="K3">
-        <v>4.200723</v>
+        <v>4.2179229999999999</v>
       </c>
       <c r="L3">
         <f>J3/K3</f>
-        <v>3.240916623162251</v>
+        <v>3.4863680536605339</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M19" si="0">ABS(J3-D3)/D3*100</f>
-        <v>2.9039531368102778</v>
+        <f t="shared" ref="M3:M19" si="2">ABS(J3-D3)/D3*100</f>
+        <v>2.2616968011126546</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N19" si="1">ABS(K3-E3)/E3*100</f>
-        <v>7.7108461538461555</v>
+        <f t="shared" ref="N3:N19" si="3">ABS(K3-E3)/E3*100</f>
+        <v>2.5883833718244853</v>
       </c>
       <c r="O3">
-        <f>(ABS(L3-G3)/G3)*100</f>
-        <v>4.4627752809313854</v>
+        <f t="shared" si="0"/>
+        <v>4.9789546060508467</v>
       </c>
       <c r="P3">
-        <f>(F3/C3)*100</f>
-        <v>85.995000000000005</v>
+        <f t="shared" si="1"/>
+        <v>89.461781609195427</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -650,57 +650,57 @@
         <v>60</v>
       </c>
       <c r="B4">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="C4">
         <f>A4*B4</f>
-        <v>76.2</v>
+        <v>78.600000000000009</v>
       </c>
       <c r="D4">
-        <v>16.079999999999998</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="E4" s="3">
-        <v>4.2</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F4">
         <f>D4*E4</f>
-        <v>67.536000000000001</v>
+        <v>70.338599999999985</v>
       </c>
       <c r="G4">
         <f>D4/E4</f>
-        <v>3.8285714285714278</v>
+        <v>4.1038647342995169</v>
       </c>
       <c r="H4">
-        <v>30.799910000000001</v>
+        <v>30.411446000000002</v>
       </c>
       <c r="I4">
-        <v>7.8468109999999998</v>
+        <v>7.3849530000000003</v>
       </c>
       <c r="J4">
-        <v>16.422968000000001</v>
+        <v>17.256174000000001</v>
       </c>
       <c r="K4">
-        <v>4.1840359999999999</v>
+        <v>4.1903969999999999</v>
       </c>
       <c r="L4">
         <f>J4/K4</f>
-        <v>3.9251497836060687</v>
+        <v>4.1180284350146303</v>
       </c>
       <c r="M4">
+        <f t="shared" si="2"/>
+        <v>1.5666509711595236</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="3"/>
+        <v>1.2173188405797164</v>
+      </c>
+      <c r="O4">
         <f t="shared" si="0"/>
-        <v>2.1328855721393198</v>
-      </c>
-      <c r="N4">
+        <v>0.34513078846715439</v>
+      </c>
+      <c r="P4">
         <f t="shared" si="1"/>
-        <v>0.38009523809524548</v>
-      </c>
-      <c r="O4">
-        <f>(ABS(L4-G4)/G4)*100</f>
-        <v>2.5225689747853957</v>
-      </c>
-      <c r="P4">
-        <f>(F4/C4)*100</f>
-        <v>88.629921259842519</v>
+        <v>89.489312977099218</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -708,57 +708,57 @@
         <v>60</v>
       </c>
       <c r="B5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C4:C5" si="2">A5*B5</f>
-        <v>81.600000000000009</v>
+        <f t="shared" ref="C5" si="4">A5*B5</f>
+        <v>81</v>
       </c>
       <c r="D5">
-        <v>17.55</v>
+        <v>17.78</v>
       </c>
       <c r="E5">
-        <v>4.1500000000000004</v>
+        <v>4.09</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F4:F5" si="3">D5*E5</f>
-        <v>72.83250000000001</v>
+        <f t="shared" ref="F5" si="5">D5*E5</f>
+        <v>72.720200000000006</v>
       </c>
       <c r="G5">
-        <f t="shared" ref="G4:G5" si="4">D5/E5</f>
-        <v>4.2289156626506026</v>
+        <f t="shared" ref="G5" si="6">D5/E5</f>
+        <v>4.3471882640586799</v>
       </c>
       <c r="H5">
-        <v>30.412991000000002</v>
+        <v>30.412125</v>
       </c>
       <c r="I5">
-        <v>7.0811440000000001</v>
+        <v>7.033544</v>
       </c>
       <c r="J5">
-        <v>17.876021999999999</v>
+        <v>18.053395999999999</v>
       </c>
       <c r="K5">
-        <v>4.1621259999999998</v>
+        <v>4.175287</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L4:L5" si="5">J5/K5</f>
-        <v>4.2949257182507212</v>
+        <f t="shared" ref="L5" si="7">J5/K5</f>
+        <v>4.323869472924855</v>
       </c>
       <c r="M5">
+        <f t="shared" si="2"/>
+        <v>1.5376602924634319</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>2.0852567237163844</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="0"/>
-        <v>1.8576752136752035</v>
-      </c>
-      <c r="N5">
+        <v>0.53641088716166263</v>
+      </c>
+      <c r="P5">
         <f t="shared" si="1"/>
-        <v>0.29219277108432323</v>
-      </c>
-      <c r="O5">
-        <f>(ABS(L5-G5)/G5)*100</f>
-        <v>1.560921542680868</v>
-      </c>
-      <c r="P5">
-        <f>(F5/C5)*100</f>
-        <v>89.255514705882348</v>
+        <v>89.778024691358027</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -766,57 +766,57 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="C6">
         <f>A6*B6</f>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D6">
-        <v>19.13</v>
+        <v>18.53</v>
       </c>
       <c r="E6">
-        <v>4.1100000000000003</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F6">
         <f>D6*E6</f>
-        <v>78.624300000000005</v>
+        <v>75.972999999999999</v>
       </c>
       <c r="G6">
         <f>D6/E6</f>
-        <v>4.6545012165450119</v>
+        <v>4.5195121951219521</v>
       </c>
       <c r="H6">
-        <v>30.409344000000001</v>
+        <v>30.408638</v>
       </c>
       <c r="I6">
-        <v>6.4616020000000001</v>
+        <v>6.7417230000000004</v>
       </c>
       <c r="J6">
-        <v>19.423361</v>
+        <v>18.770275000000002</v>
       </c>
       <c r="K6">
-        <v>4.1272190000000002</v>
+        <v>4.1614490000000002</v>
       </c>
       <c r="L6">
         <f>J6/K6</f>
-        <v>4.7061619458526431</v>
+        <v>4.510514246359862</v>
       </c>
       <c r="M6">
+        <f t="shared" si="2"/>
+        <v>1.2966810577442009</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>1.4987560975609886</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="0"/>
-        <v>1.5335128071092572</v>
-      </c>
-      <c r="N6">
+        <v>0.19909114908024605</v>
+      </c>
+      <c r="P6">
         <f t="shared" si="1"/>
-        <v>0.41895377128953459</v>
-      </c>
-      <c r="O6">
-        <f>(ABS(L6-G6)/G6)*100</f>
-        <v>1.1099090300803152</v>
-      </c>
-      <c r="P6">
-        <f>(F6/C6)*100</f>
-        <v>90.372758620689666</v>
+        <v>90.444047619047623</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -824,57 +824,57 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="C7">
         <f>A7*B7</f>
-        <v>89.4</v>
+        <v>87</v>
       </c>
       <c r="D7">
-        <v>19.899999999999999</v>
+        <v>19.18</v>
       </c>
       <c r="E7">
-        <v>4.0599999999999996</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F7">
         <f>D7*E7</f>
-        <v>80.793999999999983</v>
+        <v>79.405199999999994</v>
       </c>
       <c r="G7">
         <f>D7/E7</f>
-        <v>4.9014778325123158</v>
+        <v>4.6328502415458939</v>
       </c>
       <c r="H7">
-        <v>30.411235999999999</v>
+        <v>30.799961</v>
       </c>
       <c r="I7">
-        <v>6.1737760000000002</v>
+        <v>6.5569410000000001</v>
       </c>
       <c r="J7">
-        <v>20.185144000000001</v>
+        <v>19.421268000000001</v>
       </c>
       <c r="K7">
-        <v>4.0977800000000002</v>
+        <v>4.1345539999999996</v>
       </c>
       <c r="L7">
         <f>J7/K7</f>
-        <v>4.9258730336914134</v>
+        <v>4.6973066502457108</v>
       </c>
       <c r="M7">
+        <f t="shared" si="2"/>
+        <v>1.2579144942648675</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>0.13154589371980827</v>
+      </c>
+      <c r="O7">
         <f t="shared" si="0"/>
-        <v>1.4328844221105654</v>
-      </c>
-      <c r="N7">
+        <v>1.3912905736039738</v>
+      </c>
+      <c r="P7">
         <f t="shared" si="1"/>
-        <v>0.93054187192119686</v>
-      </c>
-      <c r="O7">
-        <f>(ABS(L7-G7)/G7)*100</f>
-        <v>0.49771113963384944</v>
-      </c>
-      <c r="P7">
-        <f>(F7/C7)*100</f>
-        <v>90.373601789709141</v>
+        <v>91.2703448275862</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -882,57 +882,57 @@
         <v>60</v>
       </c>
       <c r="B8">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="C8">
         <f>A8*B8</f>
-        <v>92.4</v>
+        <v>89.4</v>
       </c>
       <c r="D8">
-        <v>20.91</v>
+        <v>20.03</v>
       </c>
       <c r="E8">
-        <v>4.0199999999999996</v>
+        <v>4.05</v>
       </c>
       <c r="F8">
         <f>D8*E8</f>
-        <v>84.058199999999985</v>
+        <v>81.121499999999997</v>
       </c>
       <c r="G8">
         <f>D8/E8</f>
-        <v>5.2014925373134338</v>
+        <v>4.9456790123456793</v>
       </c>
       <c r="H8">
-        <v>30.411804</v>
+        <v>30.411460999999999</v>
       </c>
       <c r="I8">
-        <v>5.8009050000000002</v>
+        <v>6.1545030000000001</v>
       </c>
       <c r="J8">
-        <v>21.167235999999999</v>
+        <v>20.231714</v>
       </c>
       <c r="K8">
-        <v>4.0375490000000003</v>
+        <v>4.0943820000000004</v>
       </c>
       <c r="L8">
         <f>J8/K8</f>
-        <v>5.24259544590047</v>
+        <v>4.9413352247054618</v>
       </c>
       <c r="M8">
+        <f t="shared" si="2"/>
+        <v>1.0070594108836697</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>1.0958518518518665</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="0"/>
-        <v>1.2302056432328976</v>
-      </c>
-      <c r="N8">
+        <v>8.7829954782230574E-2</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="1"/>
-        <v>0.43654228855723148</v>
-      </c>
-      <c r="O8">
-        <f>(ABS(L8-G8)/G8)*100</f>
-        <v>0.7902137375412992</v>
-      </c>
-      <c r="P8">
-        <f>(F8/C8)*100</f>
-        <v>90.972077922077901</v>
+        <v>90.739932885906029</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -940,57 +940,57 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:C12" si="6">A9*B9</f>
-        <v>94.2</v>
+        <f t="shared" ref="C9:C12" si="8">A9*B9</f>
+        <v>93</v>
       </c>
       <c r="D9">
-        <v>21.94</v>
+        <v>20.98</v>
       </c>
       <c r="E9">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="F9">
-        <f t="shared" ref="F9:F12" si="7">D9*E9</f>
-        <v>86.443600000000004</v>
+        <f t="shared" ref="F9:F12" si="9">D9*E9</f>
+        <v>84.968999999999994</v>
       </c>
       <c r="G9">
         <f>D9/E9</f>
-        <v>5.5685279187817267</v>
+        <v>5.1802469135802474</v>
       </c>
       <c r="H9">
-        <v>30.411944999999999</v>
+        <v>30.410651999999999</v>
       </c>
       <c r="I9">
-        <v>5.3981890000000003</v>
+        <v>5.7768420000000003</v>
       </c>
       <c r="J9">
-        <v>22.170598999999999</v>
+        <v>21.174361999999999</v>
       </c>
       <c r="K9">
-        <v>3.9353310000000001</v>
+        <v>4.0223060000000004</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L12" si="8">J9/K9</f>
-        <v>5.6337316988075461</v>
+        <f t="shared" ref="L9:L12" si="10">J9/K9</f>
+        <v>5.2642344963312082</v>
       </c>
       <c r="M9">
+        <f t="shared" si="2"/>
+        <v>0.92641563393707405</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>0.68380246913578879</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="0"/>
-        <v>1.0510437556973471</v>
-      </c>
-      <c r="N9">
+        <v>1.6213046241248401</v>
+      </c>
+      <c r="P9">
         <f t="shared" si="1"/>
-        <v>0.11850253807106123</v>
-      </c>
-      <c r="O9">
-        <f>(ABS(L9-G9)/G9)*100</f>
-        <v>1.1709338801354985</v>
-      </c>
-      <c r="P9">
-        <f>(F9/C9)*100</f>
-        <v>91.766029723991508</v>
+        <v>91.364516129032253</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1001,54 +1001,54 @@
         <v>1.55</v>
       </c>
       <c r="C10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="D10">
-        <v>22.82</v>
+        <v>21.73</v>
       </c>
       <c r="E10">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="F10">
-        <f t="shared" si="7"/>
-        <v>84.662199999999999</v>
+        <f t="shared" si="9"/>
+        <v>85.181600000000003</v>
       </c>
       <c r="G10">
-        <f t="shared" ref="G10:G12" si="9">D10/E10</f>
-        <v>6.1509433962264151</v>
+        <f t="shared" ref="G10:G12" si="11">D10/E10</f>
+        <v>5.5433673469387754</v>
       </c>
       <c r="H10">
-        <v>30.411777000000001</v>
+        <v>30.410862000000002</v>
       </c>
       <c r="I10">
-        <v>5.0282859999999996</v>
+        <v>5.4749930000000004</v>
       </c>
       <c r="J10">
-        <v>23.001207000000001</v>
+        <v>21.89076</v>
       </c>
       <c r="K10">
-        <v>3.8030219999999999</v>
+        <v>3.941084</v>
       </c>
       <c r="L10">
-        <f t="shared" si="8"/>
-        <v>6.0481393481289354</v>
+        <f t="shared" si="10"/>
+        <v>5.554502263844161</v>
       </c>
       <c r="M10">
+        <f t="shared" si="2"/>
+        <v>0.73980671882190419</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>0.53785714285714548</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="0"/>
-        <v>0.79407099035933637</v>
-      </c>
-      <c r="N10">
+        <v>0.2008691866963255</v>
+      </c>
+      <c r="P10">
         <f t="shared" si="1"/>
-        <v>2.5073315363881385</v>
-      </c>
-      <c r="O10">
-        <f>(ABS(L10-G10)/G10)*100</f>
-        <v>1.6713541561860192</v>
-      </c>
-      <c r="P10">
-        <f>(F10/C10)*100</f>
-        <v>91.034623655913975</v>
+        <v>91.593118279569893</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1056,57 +1056,57 @@
         <v>60</v>
       </c>
       <c r="B11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="C11">
-        <f t="shared" si="6"/>
-        <v>93</v>
+        <f t="shared" si="8"/>
+        <v>93.600000000000009</v>
       </c>
       <c r="D11">
-        <v>23.59</v>
+        <v>22.35</v>
       </c>
       <c r="E11">
-        <v>3.61</v>
+        <v>3.84</v>
       </c>
       <c r="F11">
-        <f t="shared" si="7"/>
-        <v>85.159899999999993</v>
+        <f t="shared" si="9"/>
+        <v>85.823999999999998</v>
       </c>
       <c r="G11">
-        <f t="shared" si="9"/>
-        <v>6.5346260387811634</v>
+        <f t="shared" si="11"/>
+        <v>5.8203125000000009</v>
       </c>
       <c r="H11">
-        <v>30.413933</v>
+        <v>30.411788999999999</v>
       </c>
       <c r="I11">
-        <v>4.6391739999999997</v>
+        <v>5.1992580000000004</v>
       </c>
       <c r="J11">
-        <v>23.763169999999999</v>
+        <v>22.502890000000001</v>
       </c>
       <c r="K11">
-        <v>3.6247039999999999</v>
+        <v>3.847137</v>
       </c>
       <c r="L11">
-        <f t="shared" si="8"/>
-        <v>6.5558925639169434</v>
+        <f t="shared" si="10"/>
+        <v>5.8492562131268011</v>
       </c>
       <c r="M11">
+        <f t="shared" si="2"/>
+        <v>0.6840715883668872</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>0.18585937500000446</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="0"/>
-        <v>0.7340822382365364</v>
-      </c>
-      <c r="N11">
+        <v>0.49728795707790974</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="1"/>
-        <v>0.40731301939058312</v>
-      </c>
-      <c r="O11">
-        <f>(ABS(L11-G11)/G11)*100</f>
-        <v>0.32544364451108831</v>
-      </c>
-      <c r="P11">
-        <f>(F11/C11)*100</f>
-        <v>91.569784946236553</v>
+        <v>91.692307692307679</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1114,57 +1114,57 @@
         <v>60</v>
       </c>
       <c r="B12">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="C12">
-        <f t="shared" si="6"/>
-        <v>88.2</v>
+        <f t="shared" si="8"/>
+        <v>92.4</v>
       </c>
       <c r="D12">
-        <v>24.46</v>
+        <v>22.98</v>
       </c>
       <c r="E12">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="F12">
-        <f t="shared" si="7"/>
-        <v>80.962600000000009</v>
+        <f t="shared" si="9"/>
+        <v>85.02600000000001</v>
       </c>
       <c r="G12">
-        <f t="shared" si="9"/>
-        <v>7.3897280966767376</v>
+        <f t="shared" si="11"/>
+        <v>6.2108108108108109</v>
       </c>
       <c r="H12">
-        <v>30.411733999999999</v>
+        <v>30.411107999999999</v>
       </c>
       <c r="I12">
-        <v>4.1454120000000003</v>
+        <v>4.8993520000000004</v>
       </c>
       <c r="J12">
-        <v>24.581302999999998</v>
+        <v>23.111118000000001</v>
       </c>
       <c r="K12">
-        <v>3.3506680000000002</v>
+        <v>3.7232940000000001</v>
       </c>
       <c r="L12">
-        <f t="shared" si="8"/>
-        <v>7.3362395200001904</v>
+        <f t="shared" si="10"/>
+        <v>6.2071697803074377</v>
       </c>
       <c r="M12">
+        <f t="shared" si="2"/>
+        <v>0.5705744125326403</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>0.6295675675675656</v>
+      </c>
+      <c r="O12">
         <f t="shared" si="0"/>
-        <v>0.4959239574815924</v>
-      </c>
-      <c r="N12">
+        <v>5.8624076860229392E-2</v>
+      </c>
+      <c r="P12">
         <f t="shared" si="1"/>
-        <v>1.2286404833836904</v>
-      </c>
-      <c r="O12">
-        <f>(ABS(L12-G12)/G12)*100</f>
-        <v>0.72382333932694642</v>
-      </c>
-      <c r="P12">
-        <f>(F12/C12)*100</f>
-        <v>91.79433106575965</v>
+        <v>92.019480519480524</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1172,57 +1172,57 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="C13">
         <f>A13*B13</f>
-        <v>82.2</v>
+        <v>91.2</v>
       </c>
       <c r="D13">
-        <v>25.22</v>
+        <v>23.55</v>
       </c>
       <c r="E13">
-        <v>2.97</v>
+        <v>3.55</v>
       </c>
       <c r="F13">
         <f>D13*E13</f>
-        <v>74.903400000000005</v>
+        <v>83.602499999999992</v>
       </c>
       <c r="G13">
         <f>D13/E13</f>
-        <v>8.4915824915824913</v>
+        <v>6.6338028169014089</v>
       </c>
       <c r="H13">
-        <v>30.412528999999999</v>
+        <v>30.409915999999999</v>
       </c>
       <c r="I13">
-        <v>3.6168800000000001</v>
+        <v>4.5909089999999999</v>
       </c>
       <c r="J13">
-        <v>25.310092999999998</v>
+        <v>23.679566999999999</v>
       </c>
       <c r="K13">
-        <v>3.010062</v>
+        <v>3.5748449999999998</v>
       </c>
       <c r="L13">
         <f>J13/K13</f>
-        <v>8.4084955725164452</v>
+        <v>6.6239422967988819</v>
       </c>
       <c r="M13">
+        <f t="shared" si="2"/>
+        <v>0.55017834394903609</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>0.69985915492957762</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="0"/>
-        <v>0.35722839016653263</v>
-      </c>
-      <c r="N13">
+        <v>0.14864053657737128</v>
+      </c>
+      <c r="P13">
         <f t="shared" si="1"/>
-        <v>1.3488888888888828</v>
-      </c>
-      <c r="O13">
-        <f>(ABS(L13-G13)/G13)*100</f>
-        <v>0.97846213174526997</v>
-      </c>
-      <c r="P13">
-        <f>(F13/C13)*100</f>
-        <v>91.123357664233581</v>
+        <v>91.669407894736835</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1230,57 +1230,57 @@
         <v>60</v>
       </c>
       <c r="B14">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="C14">
         <f>A14*B14</f>
-        <v>74.400000000000006</v>
+        <v>87</v>
       </c>
       <c r="D14">
-        <v>25.83</v>
+        <v>24.35</v>
       </c>
       <c r="E14" s="3">
-        <v>2.61</v>
+        <v>3.27</v>
       </c>
       <c r="F14">
         <f>D14*E14</f>
-        <v>67.416299999999993</v>
+        <v>79.624500000000012</v>
       </c>
       <c r="G14">
         <f>D14/E14</f>
-        <v>9.8965517241379306</v>
+        <v>7.4464831804281353</v>
       </c>
       <c r="H14">
-        <v>30.412239</v>
+        <v>30.410357999999999</v>
       </c>
       <c r="I14">
-        <v>3.1199020000000002</v>
+        <v>4.1174379999999999</v>
       </c>
       <c r="J14">
-        <v>25.861650000000001</v>
+        <v>24.440062999999999</v>
       </c>
       <c r="K14">
-        <v>2.6530710000000002</v>
+        <v>3.3090850000000001</v>
       </c>
       <c r="L14">
         <f>J14/K14</f>
-        <v>9.7478167753520353</v>
+        <v>7.3857465130088826</v>
       </c>
       <c r="M14">
+        <f t="shared" si="2"/>
+        <v>0.36986858316220578</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>1.1952599388379215</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="0"/>
-        <v>0.1225319396051205</v>
-      </c>
-      <c r="N14">
+        <v>0.81564230990125741</v>
+      </c>
+      <c r="P14">
         <f t="shared" si="1"/>
-        <v>1.6502298850574832</v>
-      </c>
-      <c r="O14">
-        <f>(ABS(L14-G14)/G14)*100</f>
-        <v>1.5028966950491167</v>
-      </c>
-      <c r="P14">
-        <f>(F14/C14)*100</f>
-        <v>90.613306451612885</v>
+        <v>91.522413793103468</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1288,57 +1288,57 @@
         <v>60</v>
       </c>
       <c r="B15">
-        <v>1.1200000000000001</v>
+        <v>1.39</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:C16" si="10">A15*B15</f>
-        <v>67.2</v>
+        <f t="shared" ref="C15:C16" si="12">A15*B15</f>
+        <v>83.399999999999991</v>
       </c>
       <c r="D15">
-        <v>26.27</v>
+        <v>24.9</v>
       </c>
       <c r="E15">
-        <v>2.2999999999999998</v>
+        <v>3.06</v>
       </c>
       <c r="F15">
-        <f t="shared" ref="F15:F16" si="11">D15*E15</f>
-        <v>60.420999999999992</v>
+        <f t="shared" ref="F15:F16" si="13">D15*E15</f>
+        <v>76.194000000000003</v>
       </c>
       <c r="G15">
-        <f t="shared" ref="G15:G16" si="12">D15/E15</f>
-        <v>11.421739130434784</v>
+        <f t="shared" ref="G15:G16" si="14">D15/E15</f>
+        <v>8.1372549019607838</v>
       </c>
       <c r="H15">
-        <v>30.414455</v>
+        <v>30.410532</v>
       </c>
       <c r="I15">
-        <v>2.7397300000000002</v>
+        <v>3.747369</v>
       </c>
       <c r="J15">
-        <v>26.282420999999999</v>
+        <v>24.939965999999998</v>
       </c>
       <c r="K15">
-        <v>2.3675169999999999</v>
+        <v>3.0732529999999998</v>
       </c>
       <c r="L15">
-        <f t="shared" ref="L15:L16" si="13">J15/K15</f>
-        <v>11.101259674164959</v>
+        <f t="shared" ref="L15:L16" si="15">J15/K15</f>
+        <v>8.1151685201316006</v>
       </c>
       <c r="M15">
+        <f t="shared" si="2"/>
+        <v>0.16050602409638445</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>0.43310457516339013</v>
+      </c>
+      <c r="O15">
         <f t="shared" si="0"/>
-        <v>4.7282070803196782E-2</v>
-      </c>
-      <c r="N15">
+        <v>0.27142300561164912</v>
+      </c>
+      <c r="P15">
         <f t="shared" si="1"/>
-        <v>2.9355217391304369</v>
-      </c>
-      <c r="O15">
-        <f>(ABS(L15-G15)/G15)*100</f>
-        <v>2.805872666237518</v>
-      </c>
-      <c r="P15">
-        <f>(F15/C15)*100</f>
-        <v>89.912202380952365</v>
+        <v>91.359712230215834</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1346,57 +1346,57 @@
         <v>60</v>
       </c>
       <c r="B16">
-        <v>0.93</v>
+        <v>1.31</v>
       </c>
       <c r="C16">
-        <f t="shared" si="10"/>
-        <v>55.800000000000004</v>
+        <f t="shared" si="12"/>
+        <v>78.600000000000009</v>
       </c>
       <c r="D16">
-        <v>26.65</v>
+        <v>25.25</v>
       </c>
       <c r="E16">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="F16">
-        <f t="shared" si="11"/>
-        <v>49.835500000000003</v>
+        <f t="shared" si="13"/>
+        <v>71.709999999999994</v>
       </c>
       <c r="G16">
-        <f t="shared" si="12"/>
-        <v>14.251336898395721</v>
+        <f t="shared" si="14"/>
+        <v>8.8908450704225359</v>
       </c>
       <c r="H16">
-        <v>30.413723000000001</v>
+        <v>30.412103999999999</v>
       </c>
       <c r="I16">
-        <v>2.2251089999999998</v>
+        <v>3.4818790000000002</v>
       </c>
       <c r="J16">
-        <v>26.626436000000002</v>
+        <v>25.292833000000002</v>
       </c>
       <c r="K16">
-        <v>1.948026</v>
+        <v>2.8957739999999998</v>
       </c>
       <c r="L16">
-        <f t="shared" si="13"/>
-        <v>13.668419210010544</v>
+        <f t="shared" si="15"/>
+        <v>8.7343946730649566</v>
       </c>
       <c r="M16">
+        <f t="shared" si="2"/>
+        <v>0.16963564356436309</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>1.9638732394366194</v>
+      </c>
+      <c r="O16">
         <f t="shared" si="0"/>
-        <v>8.8420262664153135E-2</v>
-      </c>
-      <c r="N16">
+        <v>1.7596797168139606</v>
+      </c>
+      <c r="P16">
         <f t="shared" si="1"/>
-        <v>4.1725133689839531</v>
-      </c>
-      <c r="O16">
-        <f>(ABS(L16-G16)/G16)*100</f>
-        <v>4.090266706492609</v>
-      </c>
-      <c r="P16">
-        <f>(F16/C16)*100</f>
-        <v>89.310931899641574</v>
+        <v>91.234096692111947</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1404,57 +1404,57 @@
         <v>60</v>
       </c>
       <c r="B17">
-        <v>0.6</v>
+        <v>1.18</v>
       </c>
       <c r="C17">
         <f>A17*B17</f>
-        <v>36</v>
+        <v>70.8</v>
       </c>
       <c r="D17">
-        <v>27.29</v>
+        <v>25.81</v>
       </c>
       <c r="E17">
-        <v>1.1100000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="F17">
         <f>D17*E17</f>
-        <v>30.291900000000002</v>
+        <v>64.008799999999994</v>
       </c>
       <c r="G17">
         <f>D17/E17</f>
-        <v>24.585585585585584</v>
+        <v>10.407258064516128</v>
       </c>
       <c r="H17">
-        <v>30.427081999999999</v>
+        <v>30.413875999999998</v>
       </c>
       <c r="I17">
-        <v>1.4404539999999999</v>
+        <v>3.0046179999999998</v>
       </c>
       <c r="J17">
-        <v>27.169167000000002</v>
+        <v>25.808133999999999</v>
       </c>
       <c r="K17">
-        <v>1.2862199999999999</v>
+        <v>2.5496120000000002</v>
       </c>
       <c r="L17">
         <f>J17/K17</f>
-        <v>21.123265848766156</v>
+        <v>10.122377051880834</v>
       </c>
       <c r="M17">
+        <f t="shared" si="2"/>
+        <v>7.2297559085614154E-3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>2.8069354838709768</v>
+      </c>
+      <c r="O17">
         <f t="shared" si="0"/>
-        <v>0.44277390985708148</v>
-      </c>
-      <c r="N17">
+        <v>2.7373301485297534</v>
+      </c>
+      <c r="P17">
         <f t="shared" si="1"/>
-        <v>15.875675675675657</v>
-      </c>
-      <c r="O17">
-        <f>(ABS(L17-G17)/G17)*100</f>
-        <v>14.082722271416509</v>
-      </c>
-      <c r="P17">
-        <f>(F17/C17)*100</f>
-        <v>84.144166666666678</v>
+        <v>90.407909604519759</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1462,57 +1462,57 @@
         <v>60</v>
       </c>
       <c r="B18">
-        <v>0.33</v>
+        <v>1.07</v>
       </c>
       <c r="C18">
         <f>A18*B18</f>
-        <v>19.8</v>
+        <v>64.2</v>
       </c>
       <c r="D18">
-        <v>27.79</v>
+        <v>26.27</v>
       </c>
       <c r="E18">
-        <v>0.52</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F18">
         <f>D18*E18</f>
-        <v>14.450799999999999</v>
+        <v>57.794000000000004</v>
       </c>
       <c r="G18">
         <f>D18/E18</f>
-        <v>53.442307692307686</v>
+        <v>11.94090909090909</v>
       </c>
       <c r="H18">
-        <v>30.434350999999999</v>
+        <v>30.411911</v>
       </c>
       <c r="I18">
-        <v>0.80703899999999995</v>
+        <v>2.620044</v>
       </c>
       <c r="J18">
-        <v>27.623262</v>
+        <v>26.232281</v>
       </c>
       <c r="K18">
-        <v>0.73249600000000004</v>
+        <v>2.2599610000000001</v>
       </c>
       <c r="L18">
         <f>J18/K18</f>
-        <v>37.711143815119812</v>
+        <v>11.60740428706513</v>
       </c>
       <c r="M18">
+        <f t="shared" si="2"/>
+        <v>0.14358203273695916</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>2.7254999999999967</v>
+      </c>
+      <c r="O18">
         <f t="shared" si="0"/>
-        <v>0.59999280316660208</v>
-      </c>
-      <c r="N18">
+        <v>2.7929599103795653</v>
+      </c>
+      <c r="P18">
         <f t="shared" si="1"/>
-        <v>40.864615384615391</v>
-      </c>
-      <c r="O18">
-        <f>(ABS(L18-G18)/G18)*100</f>
-        <v>29.435787031801713</v>
-      </c>
-      <c r="P18">
-        <f>(F18/C18)*100</f>
-        <v>72.983838383838375</v>
+        <v>90.021806853582547</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1520,57 +1520,231 @@
         <v>60</v>
       </c>
       <c r="B19">
-        <v>0.14000000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="C19">
         <f>A19*B19</f>
-        <v>8.4</v>
+        <v>48.6</v>
       </c>
       <c r="D19">
-        <v>28.2</v>
+        <v>26.79</v>
       </c>
       <c r="E19">
-        <v>0.06</v>
+        <v>1.61</v>
       </c>
       <c r="F19">
         <f>D19*E19</f>
-        <v>1.6919999999999999</v>
+        <v>43.131900000000002</v>
       </c>
       <c r="G19">
         <f>D19/E19</f>
-        <v>470</v>
+        <v>16.63975155279503</v>
       </c>
       <c r="H19">
-        <v>30.437847000000001</v>
+        <v>30.799515</v>
       </c>
       <c r="I19">
-        <v>0.32041599999999998</v>
+        <v>1.9535499999999999</v>
       </c>
       <c r="J19">
-        <v>27.982399000000001</v>
+        <v>26.693003000000001</v>
       </c>
       <c r="K19">
-        <v>0.294568</v>
+        <v>1.693082</v>
       </c>
       <c r="L19">
         <f>J19/K19</f>
-        <v>94.994700714266315</v>
+        <v>15.765924509267714</v>
       </c>
       <c r="M19">
+        <f t="shared" si="2"/>
+        <v>0.36206420306083698</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>5.1603726708074458</v>
+      </c>
+      <c r="O19">
         <f t="shared" si="0"/>
-        <v>0.77163475177304397</v>
-      </c>
-      <c r="N19">
+        <v>5.251442852105181</v>
+      </c>
+      <c r="P19">
         <f t="shared" si="1"/>
-        <v>390.94666666666672</v>
-      </c>
-      <c r="O19">
-        <f>(ABS(L19-G19)/G19)*100</f>
-        <v>79.788361550156111</v>
-      </c>
-      <c r="P19">
-        <f>(F19/C19)*100</f>
-        <v>20.142857142857139</v>
+        <v>88.748765432098764</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>60</v>
+      </c>
+      <c r="B20">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C20">
+        <f t="shared" ref="C20:C24" si="16">A20*B20</f>
+        <v>33</v>
+      </c>
+      <c r="D20">
+        <v>27.25</v>
+      </c>
+      <c r="E20">
+        <v>1.02</v>
+      </c>
+      <c r="F20">
+        <f t="shared" ref="F20:F24" si="17">D20*E20</f>
+        <v>27.795000000000002</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ref="G20:G24" si="18">D20/E20</f>
+        <v>26.715686274509803</v>
+      </c>
+      <c r="H20">
+        <v>30.428387000000001</v>
+      </c>
+      <c r="I20">
+        <v>1.320891</v>
+      </c>
+      <c r="J20">
+        <v>27.100121999999999</v>
+      </c>
+      <c r="K20">
+        <v>1.176412</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ref="L20:L24" si="19">J20/K20</f>
+        <v>23.036250905295084</v>
+      </c>
+      <c r="M20">
+        <f t="shared" ref="M20:M24" si="20">ABS(J20-D20)/D20*100</f>
+        <v>0.55001100917431578</v>
+      </c>
+      <c r="N20">
+        <f t="shared" ref="N20:N24" si="21">ABS(K20-E20)/E20*100</f>
+        <v>15.334509803921566</v>
+      </c>
+      <c r="O20">
+        <f t="shared" ref="O20:O24" si="22">(ABS(L20-G20)/G20)*100</f>
+        <v>13.772565418711977</v>
+      </c>
+      <c r="P20">
+        <f t="shared" ref="P20:P24" si="23">(F20/C20)*100</f>
+        <v>84.227272727272734</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>60</v>
+      </c>
+      <c r="B21">
+        <v>0.35</v>
+      </c>
+      <c r="C21">
+        <f t="shared" ref="C21:C22" si="24">A21*B21</f>
+        <v>21</v>
+      </c>
+      <c r="D21">
+        <v>27.62</v>
+      </c>
+      <c r="E21">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F21">
+        <f t="shared" ref="F21:F22" si="25">D21*E21</f>
+        <v>15.743399999999999</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ref="G21:G22" si="26">D21/E21</f>
+        <v>48.456140350877199</v>
+      </c>
+      <c r="H21">
+        <v>30.434180999999999</v>
+      </c>
+      <c r="I21">
+        <v>0.84493600000000002</v>
+      </c>
+      <c r="J21">
+        <v>27.427097</v>
+      </c>
+      <c r="K21">
+        <v>0.76145099999999999</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ref="L21:L22" si="27">J21/K21</f>
+        <v>36.019516685906254</v>
+      </c>
+      <c r="M21">
+        <f t="shared" ref="M21:M22" si="28">ABS(J21-D21)/D21*100</f>
+        <v>0.69841781317886009</v>
+      </c>
+      <c r="N21">
+        <f t="shared" ref="N21:N22" si="29">ABS(K21-E21)/E21*100</f>
+        <v>33.587894736842117</v>
+      </c>
+      <c r="O21">
+        <f t="shared" ref="O21:O22" si="30">(ABS(L21-G21)/G21)*100</f>
+        <v>25.665733124668495</v>
+      </c>
+      <c r="P21">
+        <f t="shared" ref="P21:P22" si="31">(F21/C21)*100</f>
+        <v>74.968571428571423</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>60</v>
+      </c>
+      <c r="B22">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="24"/>
+        <v>8.4</v>
+      </c>
+      <c r="D22">
+        <v>28.05</v>
+      </c>
+      <c r="E22">
+        <v>0.06</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="25"/>
+        <v>1.6830000000000001</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="26"/>
+        <v>467.50000000000006</v>
+      </c>
+      <c r="H22">
+        <v>30.799423000000001</v>
+      </c>
+      <c r="I22">
+        <v>0.298323</v>
+      </c>
+      <c r="J22">
+        <v>27.814807999999999</v>
+      </c>
+      <c r="K22">
+        <v>0.26941399999999999</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="27"/>
+        <v>103.2418805258821</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="28"/>
+        <v>0.83847415329768771</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="29"/>
+        <v>349.02333333333331</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="30"/>
+        <v>77.916175288581371</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="31"/>
+        <v>20.035714285714285</v>
       </c>
     </row>
   </sheetData>
